--- a/MRUCache/OverallStatsMRURP-noboot.xlsx
+++ b/MRUCache/OverallStatsMRURP-noboot.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alexb\OneDrive\Documents\Thesis\MRUCache\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B3E3105-0447-4BC2-AA5D-F59014CB7E57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF19CB48-2A6C-4966-A8AB-6E61A3189DA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="1830" windowWidth="38640" windowHeight="21840" xr2:uid="{10219E88-FFE1-4721-B87F-58FBE8BDB343}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{10219E88-FFE1-4721-B87F-58FBE8BDB343}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="39">
   <si>
     <t>MRURP</t>
   </si>
@@ -524,7 +524,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{263ED5F6-01AE-4A3B-A6DC-B2A5E21A756E}">
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:M33"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.81640625" customWidth="1"/>
@@ -633,10 +633,10 @@
         <v>2</v>
       </c>
       <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
         <v>2</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
       </c>
       <c r="F4">
         <v>41</v>
@@ -645,12 +645,12 @@
         <v>95.5555555555555</v>
       </c>
       <c r="H4">
-        <f t="shared" ref="H4:H12" si="0">(C4)/(C4+D4)</f>
-        <v>0.5</v>
+        <f t="shared" ref="H4:H13" si="0">(C4)/(C4+D4)</f>
+        <v>1</v>
       </c>
       <c r="I4">
         <f t="shared" ref="I4:I13" si="1">C4/(C4+E4)</f>
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J4">
         <f t="shared" ref="J4:J13" si="2">(2*(H4*I4))/(H4+I4)</f>
@@ -658,7 +658,7 @@
       </c>
       <c r="K4">
         <f t="shared" ref="K4:K13" si="3">F4/(F4+D4)</f>
-        <v>0.95348837209302328</v>
+        <v>1</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -678,10 +678,10 @@
         <v>3</v>
       </c>
       <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5">
         <v>3</v>
-      </c>
-      <c r="E5">
-        <v>2</v>
       </c>
       <c r="F5">
         <v>36</v>
@@ -691,11 +691,11 @@
       </c>
       <c r="H5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="I5">
         <f t="shared" si="1"/>
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J5">
         <f t="shared" si="2"/>
@@ -703,7 +703,7 @@
       </c>
       <c r="K5">
         <f t="shared" si="3"/>
-        <v>0.92307692307692313</v>
+        <v>0.94736842105263153</v>
       </c>
       <c r="L5">
         <v>10</v>
@@ -723,10 +723,10 @@
         <v>6</v>
       </c>
       <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
         <v>4</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
       </c>
       <c r="F6">
         <v>267</v>
@@ -736,11 +736,11 @@
       </c>
       <c r="H6">
         <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="I6">
         <f t="shared" si="1"/>
-        <v>0.8571428571428571</v>
+        <v>0.6</v>
       </c>
       <c r="J6">
         <f t="shared" si="2"/>
@@ -748,7 +748,7 @@
       </c>
       <c r="K6">
         <f t="shared" si="3"/>
-        <v>0.98523985239852396</v>
+        <v>0.99626865671641796</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -768,10 +768,10 @@
         <v>20</v>
       </c>
       <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
         <v>4</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
       </c>
       <c r="F7">
         <v>1331</v>
@@ -781,11 +781,11 @@
       </c>
       <c r="H7">
         <f t="shared" si="0"/>
-        <v>0.83333333333333337</v>
+        <v>0.95238095238095233</v>
       </c>
       <c r="I7">
         <f t="shared" si="1"/>
-        <v>0.95238095238095233</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="J7">
         <f t="shared" si="2"/>
@@ -793,7 +793,7 @@
       </c>
       <c r="K7">
         <f t="shared" si="3"/>
-        <v>0.99700374531835201</v>
+        <v>0.99924924924924929</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -813,10 +813,10 @@
         <v>2</v>
       </c>
       <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
         <v>2</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
       </c>
       <c r="F8">
         <v>137</v>
@@ -826,11 +826,11 @@
       </c>
       <c r="H8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I8">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J8">
         <f t="shared" si="2"/>
@@ -838,7 +838,7 @@
       </c>
       <c r="K8">
         <f t="shared" si="3"/>
-        <v>0.98561151079136688</v>
+        <v>1</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -858,10 +858,10 @@
         <v>1</v>
       </c>
       <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
         <v>3</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
       </c>
       <c r="F9">
         <v>36</v>
@@ -871,11 +871,11 @@
       </c>
       <c r="H9">
         <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I9">
+        <f t="shared" si="1"/>
         <v>0.25</v>
-      </c>
-      <c r="I9">
-        <f>C9/(C9+E9)</f>
-        <v>1</v>
       </c>
       <c r="J9">
         <f>(2*(H9*I9))/(H9+I9)</f>
@@ -883,7 +883,7 @@
       </c>
       <c r="K9">
         <f t="shared" si="3"/>
-        <v>0.92307692307692313</v>
+        <v>1</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -903,10 +903,10 @@
         <v>0</v>
       </c>
       <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
         <v>16</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
       </c>
       <c r="F10">
         <v>198</v>
@@ -914,13 +914,13 @@
       <c r="G10">
         <v>92.523364485981304</v>
       </c>
-      <c r="H10">
+      <c r="H10" t="e">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I10" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I10">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="J10" t="e">
         <f t="shared" si="2"/>
@@ -928,7 +928,7 @@
       </c>
       <c r="K10">
         <f t="shared" si="3"/>
-        <v>0.92523364485981308</v>
+        <v>1</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -1013,7 +1013,7 @@
         <v>1</v>
       </c>
       <c r="J12">
-        <f t="shared" si="2"/>
+        <f>(2*(H12*I12))/(H12+I12)</f>
         <v>1</v>
       </c>
       <c r="K12">
@@ -1038,10 +1038,10 @@
         <v>3</v>
       </c>
       <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
         <v>2</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
       </c>
       <c r="F13">
         <v>29</v>
@@ -1050,12 +1050,12 @@
         <v>94.117647059999996</v>
       </c>
       <c r="H13">
-        <f>(C13)/(C13+D13)</f>
-        <v>0.6</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="I13">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J13">
         <f t="shared" si="2"/>
@@ -1063,7 +1063,7 @@
       </c>
       <c r="K13">
         <f t="shared" si="3"/>
-        <v>0.93548387096774188</v>
+        <v>1</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -1083,10 +1083,10 @@
         <v>0</v>
       </c>
       <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
         <v>12</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
       </c>
       <c r="F14">
         <v>114</v>
@@ -1095,19 +1095,19 @@
         <v>90.47619048</v>
       </c>
       <c r="H14">
-        <f t="shared" ref="H14:H15" si="4">(C14)/(C14+D14)</f>
+        <f>(C14)/(C14+E14)</f>
         <v>0</v>
       </c>
       <c r="I14" t="e">
-        <f t="shared" ref="I14:I15" si="5">C14/(C14+E14)</f>
+        <f>C14/(C14+D14)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J14" t="e">
-        <f t="shared" ref="J14:J15" si="6">(2*(H14*I14))/(H14+I14)</f>
+        <f t="shared" ref="J14:J15" si="4">(2*(H14*I14))/(H14+I14)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="K14">
-        <f t="shared" ref="K14:K15" si="7">F14/(F14+D14)</f>
+        <f>F14/(F14+E14)</f>
         <v>0.90476190476190477</v>
       </c>
       <c r="L14">
@@ -1128,10 +1128,10 @@
         <v>253</v>
       </c>
       <c r="D15">
+        <v>16</v>
+      </c>
+      <c r="E15">
         <v>249</v>
-      </c>
-      <c r="E15">
-        <v>16</v>
       </c>
       <c r="F15">
         <v>5001</v>
@@ -1140,25 +1140,337 @@
         <v>95.198405510000001</v>
       </c>
       <c r="H15">
+        <f>(C15)/(C15+E15)</f>
+        <v>0.50398406374501992</v>
+      </c>
+      <c r="I15">
+        <f>C15/(C15+D15)</f>
+        <v>0.94052044609665431</v>
+      </c>
+      <c r="J15">
         <f t="shared" si="4"/>
+        <v>0.6562905317769131</v>
+      </c>
+      <c r="K15">
+        <f>F15/(F15+E15)</f>
+        <v>0.95257142857142862</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>12</v>
+      </c>
+      <c r="B22">
+        <v>95.5555555555555</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22">
+        <v>0.5</v>
+      </c>
+      <c r="E22">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23">
+        <v>88.636363636363598</v>
+      </c>
+      <c r="C23">
+        <v>0.6</v>
+      </c>
+      <c r="D23">
+        <v>0.5</v>
+      </c>
+      <c r="E23">
+        <v>0.54545454545454541</v>
+      </c>
+      <c r="F23">
+        <v>0.94736842105263153</v>
+      </c>
+      <c r="G23">
+        <v>10</v>
+      </c>
+      <c r="H23">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>17</v>
+      </c>
+      <c r="B24">
+        <v>98.201438850000002</v>
+      </c>
+      <c r="C24">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="D24">
+        <v>0.6</v>
+      </c>
+      <c r="E24">
+        <v>0.70588235294117641</v>
+      </c>
+      <c r="F24">
+        <v>0.99626865671641796</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>19</v>
+      </c>
+      <c r="B25">
+        <v>99.631268436578097</v>
+      </c>
+      <c r="C25">
+        <v>0.95238095238095233</v>
+      </c>
+      <c r="D25">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="E25">
+        <v>0.88888888888888895</v>
+      </c>
+      <c r="F25">
+        <v>0.99924924924924929</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>21</v>
+      </c>
+      <c r="B26">
+        <v>98.581560283687907</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+      <c r="D26">
+        <v>0.5</v>
+      </c>
+      <c r="E26">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F26">
+        <v>1</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>23</v>
+      </c>
+      <c r="B27">
+        <v>92.5</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+      <c r="D27">
+        <v>0.25</v>
+      </c>
+      <c r="E27">
+        <v>0.4</v>
+      </c>
+      <c r="F27">
+        <v>1</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>25</v>
+      </c>
+      <c r="B28">
+        <v>92.523364485981304</v>
+      </c>
+      <c r="C28" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D28">
+        <v>0</v>
+      </c>
+      <c r="E28" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F28">
+        <v>1</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>26</v>
+      </c>
+      <c r="B29">
+        <v>87.878787878787804</v>
+      </c>
+      <c r="C29">
+        <v>0.5</v>
+      </c>
+      <c r="D29">
+        <v>0.5</v>
+      </c>
+      <c r="E29">
+        <v>0.5</v>
+      </c>
+      <c r="F29">
+        <v>0.93103448275862066</v>
+      </c>
+      <c r="G29">
+        <v>10</v>
+      </c>
+      <c r="H29">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>28</v>
+      </c>
+      <c r="B30">
+        <v>100</v>
+      </c>
+      <c r="C30">
+        <v>1</v>
+      </c>
+      <c r="D30">
+        <v>1</v>
+      </c>
+      <c r="E30">
+        <v>1</v>
+      </c>
+      <c r="F30">
+        <v>1</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>29</v>
+      </c>
+      <c r="B31">
+        <v>94.117647059999996</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
+      </c>
+      <c r="D31">
+        <v>0.6</v>
+      </c>
+      <c r="E31">
+        <v>0.74999999999999989</v>
+      </c>
+      <c r="F31">
+        <v>1</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>30</v>
+      </c>
+      <c r="B32">
+        <v>90.47619048</v>
+      </c>
+      <c r="C32">
+        <v>0</v>
+      </c>
+      <c r="D32" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E32" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F32">
+        <v>0.90476190476190477</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>32</v>
+      </c>
+      <c r="B33">
+        <v>95.198405510000001</v>
+      </c>
+      <c r="C33">
         <v>0.50398406374501992</v>
       </c>
-      <c r="I15">
-        <f t="shared" si="5"/>
+      <c r="D33">
         <v>0.94052044609665431</v>
       </c>
-      <c r="J15">
-        <f t="shared" si="6"/>
+      <c r="E33">
         <v>0.6562905317769131</v>
       </c>
-      <c r="K15">
-        <f t="shared" si="7"/>
+      <c r="F33">
         <v>0.95257142857142862</v>
       </c>
-      <c r="L15">
-        <v>0</v>
-      </c>
-      <c r="M15">
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
         <v>40</v>
       </c>
     </row>

--- a/MRUCache/OverallStatsMRURP-noboot.xlsx
+++ b/MRUCache/OverallStatsMRURP-noboot.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alexb\OneDrive\Documents\Thesis\MRUCache\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF19CB48-2A6C-4966-A8AB-6E61A3189DA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46EF091F-7B86-4D83-B61C-CE94C6A6AA9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{10219E88-FFE1-4721-B87F-58FBE8BDB343}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{10219E88-FFE1-4721-B87F-58FBE8BDB343}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="40">
   <si>
     <t>MRURP</t>
   </si>
@@ -153,6 +153,9 @@
   </si>
   <si>
     <t>Nu: 0.5, Gamma: 0.99</t>
+  </si>
+  <si>
+    <t>Balanced Accuracy</t>
   </si>
 </sst>
 </file>
@@ -524,19 +527,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{263ED5F6-01AE-4A3B-A6DC-B2A5E21A756E}">
-  <dimension ref="A1:M33"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:N33"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.81640625" customWidth="1"/>
-    <col min="2" max="2" width="21.26953125" customWidth="1"/>
+    <col min="1" max="1" width="19.77734375" customWidth="1"/>
+    <col min="2" max="2" width="21.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -576,8 +579,11 @@
       <c r="M2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -621,8 +627,12 @@
       <c r="M3">
         <v>40</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N3">
+        <f>(I3+K3)/2</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -666,8 +676,12 @@
       <c r="M4">
         <v>40</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N4">
+        <f t="shared" ref="N4:N15" si="4">(I4+K4)/2</f>
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -711,8 +725,12 @@
       <c r="M5">
         <v>40</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N5">
+        <f t="shared" si="4"/>
+        <v>0.72368421052631571</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -756,8 +774,12 @@
       <c r="M6">
         <v>40</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N6">
+        <f t="shared" si="4"/>
+        <v>0.79813432835820897</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -801,8 +823,12 @@
       <c r="M7">
         <v>40</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N7">
+        <f t="shared" si="4"/>
+        <v>0.91629129129129128</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -846,8 +872,12 @@
       <c r="M8">
         <v>40</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N8">
+        <f t="shared" si="4"/>
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -891,8 +921,12 @@
       <c r="M9">
         <v>40</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N9">
+        <f t="shared" si="4"/>
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -936,8 +970,12 @@
       <c r="M10">
         <v>40</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N10">
+        <f t="shared" si="4"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>26</v>
       </c>
@@ -981,8 +1019,12 @@
       <c r="M11">
         <v>40</v>
       </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N11">
+        <f t="shared" si="4"/>
+        <v>0.71551724137931028</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -1026,8 +1068,12 @@
       <c r="M12">
         <v>40</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N12">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>29</v>
       </c>
@@ -1071,8 +1117,12 @@
       <c r="M13">
         <v>40</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N13">
+        <f t="shared" si="4"/>
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>30</v>
       </c>
@@ -1103,7 +1153,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="J14" t="e">
-        <f t="shared" ref="J14:J15" si="4">(2*(H14*I14))/(H14+I14)</f>
+        <f t="shared" ref="J14:J15" si="5">(2*(H14*I14))/(H14+I14)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="K14">
@@ -1116,8 +1166,12 @@
       <c r="M14">
         <v>40</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N14" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>32</v>
       </c>
@@ -1148,7 +1202,7 @@
         <v>0.94052044609665431</v>
       </c>
       <c r="J15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.6562905317769131</v>
       </c>
       <c r="K15">
@@ -1161,8 +1215,12 @@
       <c r="M15">
         <v>40</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="N15">
+        <f t="shared" si="4"/>
+        <v>0.94654593733404147</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>12</v>
       </c>
@@ -1188,7 +1246,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>14</v>
       </c>
@@ -1214,7 +1272,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>17</v>
       </c>
@@ -1240,7 +1298,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>19</v>
       </c>
@@ -1266,7 +1324,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>21</v>
       </c>
@@ -1292,7 +1350,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>23</v>
       </c>
@@ -1318,7 +1376,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>25</v>
       </c>
@@ -1344,7 +1402,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>26</v>
       </c>
@@ -1370,7 +1428,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>28</v>
       </c>
@@ -1396,7 +1454,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>29</v>
       </c>
@@ -1422,7 +1480,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>30</v>
       </c>
@@ -1448,7 +1506,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>32</v>
       </c>

--- a/MRUCache/OverallStatsMRURP-noboot.xlsx
+++ b/MRUCache/OverallStatsMRURP-noboot.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alexb\OneDrive\Documents\Thesis\MRUCache\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46EF091F-7B86-4D83-B61C-CE94C6A6AA9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A70E9BF2-C410-4E25-A6DF-00F512246832}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{10219E88-FFE1-4721-B87F-58FBE8BDB343}"/>
+    <workbookView xWindow="5920" yWindow="4610" windowWidth="28800" windowHeight="14460" xr2:uid="{10219E88-FFE1-4721-B87F-58FBE8BDB343}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -527,19 +527,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{263ED5F6-01AE-4A3B-A6DC-B2A5E21A756E}">
-  <dimension ref="A1:N33"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:N31"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="19.77734375" customWidth="1"/>
-    <col min="2" max="2" width="21.21875" customWidth="1"/>
+    <col min="1" max="1" width="19.81640625" customWidth="1"/>
+    <col min="2" max="2" width="21.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -583,7 +583,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -632,7 +632,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -659,7 +659,7 @@
         <v>1</v>
       </c>
       <c r="I4">
-        <f t="shared" ref="I4:I13" si="1">C4/(C4+E4)</f>
+        <f t="shared" ref="I4:I15" si="1">C4/(C4+E4)</f>
         <v>0.5</v>
       </c>
       <c r="J4">
@@ -681,7 +681,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -730,7 +730,7 @@
         <v>0.72368421052631571</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -779,7 +779,7 @@
         <v>0.79813432835820897</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -828,7 +828,7 @@
         <v>0.91629129129129128</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -877,7 +877,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -926,7 +926,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -975,7 +975,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>26</v>
       </c>
@@ -1024,7 +1024,7 @@
         <v>0.71551724137931028</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -1073,7 +1073,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>29</v>
       </c>
@@ -1122,7 +1122,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>30</v>
       </c>
@@ -1148,9 +1148,9 @@
         <f>(C14)/(C14+E14)</f>
         <v>0</v>
       </c>
-      <c r="I14" t="e">
-        <f>C14/(C14+D14)</f>
-        <v>#DIV/0!</v>
+      <c r="I14">
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="J14" t="e">
         <f t="shared" ref="J14:J15" si="5">(2*(H14*I14))/(H14+I14)</f>
@@ -1166,12 +1166,12 @@
       <c r="M14">
         <v>40</v>
       </c>
-      <c r="N14" t="e">
+      <c r="N14">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+        <v>0.45238095238095238</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>32</v>
       </c>
@@ -1198,12 +1198,12 @@
         <v>0.50398406374501992</v>
       </c>
       <c r="I15">
-        <f>C15/(C15+D15)</f>
-        <v>0.94052044609665431</v>
+        <f t="shared" si="1"/>
+        <v>0.50398406374501992</v>
       </c>
       <c r="J15">
         <f t="shared" si="5"/>
-        <v>0.6562905317769131</v>
+        <v>0.50398406374501992</v>
       </c>
       <c r="K15">
         <f>F15/(F15+E15)</f>
@@ -1217,319 +1217,247 @@
       </c>
       <c r="N15">
         <f t="shared" si="4"/>
-        <v>0.94654593733404147</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+        <v>0.72827774615822427</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20">
+        <v>95.5555555555555</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <v>0.5</v>
+      </c>
+      <c r="E20">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F20">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21">
+        <v>88.636363636363598</v>
+      </c>
+      <c r="C21">
+        <v>0.6</v>
+      </c>
+      <c r="D21">
+        <v>0.5</v>
+      </c>
+      <c r="E21">
+        <v>0.54545454545454541</v>
+      </c>
+      <c r="F21">
+        <v>0.72368421052631571</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B22">
-        <v>95.5555555555555</v>
+        <v>98.201438850000002</v>
       </c>
       <c r="C22">
-        <v>1</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="D22">
+        <v>0.6</v>
+      </c>
+      <c r="E22">
+        <v>0.70588235294117641</v>
+      </c>
+      <c r="F22">
+        <v>0.79813432835820897</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>19</v>
+      </c>
+      <c r="B23">
+        <v>99.631268436578097</v>
+      </c>
+      <c r="C23">
+        <v>0.95238095238095233</v>
+      </c>
+      <c r="D23">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="E23">
+        <v>0.88888888888888895</v>
+      </c>
+      <c r="F23">
+        <v>0.91629129129129128</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>21</v>
+      </c>
+      <c r="B24">
+        <v>98.581560283687907</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+      <c r="D24">
         <v>0.5</v>
       </c>
-      <c r="E22">
+      <c r="E24">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F22">
-        <v>1</v>
-      </c>
-      <c r="G22">
-        <v>0</v>
-      </c>
-      <c r="H22">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>14</v>
-      </c>
-      <c r="B23">
-        <v>88.636363636363598</v>
-      </c>
-      <c r="C23">
+      <c r="F24">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25">
+        <v>92.5</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
+      <c r="D25">
+        <v>0.25</v>
+      </c>
+      <c r="E25">
+        <v>0.4</v>
+      </c>
+      <c r="F25">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26">
+        <v>92.523364485981304</v>
+      </c>
+      <c r="C26" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F26">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27">
+        <v>87.878787878787804</v>
+      </c>
+      <c r="C27">
+        <v>0.5</v>
+      </c>
+      <c r="D27">
+        <v>0.5</v>
+      </c>
+      <c r="E27">
+        <v>0.5</v>
+      </c>
+      <c r="F27">
+        <v>0.71551724137931028</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>28</v>
+      </c>
+      <c r="B28">
+        <v>100</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
+      <c r="D28">
+        <v>1</v>
+      </c>
+      <c r="E28">
+        <v>1</v>
+      </c>
+      <c r="F28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>29</v>
+      </c>
+      <c r="B29">
+        <v>94.117647059999996</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
+      <c r="D29">
         <v>0.6</v>
       </c>
-      <c r="D23">
-        <v>0.5</v>
-      </c>
-      <c r="E23">
-        <v>0.54545454545454541</v>
-      </c>
-      <c r="F23">
-        <v>0.94736842105263153</v>
-      </c>
-      <c r="G23">
-        <v>10</v>
-      </c>
-      <c r="H23">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>17</v>
-      </c>
-      <c r="B24">
-        <v>98.201438850000002</v>
-      </c>
-      <c r="C24">
-        <v>0.8571428571428571</v>
-      </c>
-      <c r="D24">
-        <v>0.6</v>
-      </c>
-      <c r="E24">
-        <v>0.70588235294117641</v>
-      </c>
-      <c r="F24">
-        <v>0.99626865671641796</v>
-      </c>
-      <c r="G24">
-        <v>0</v>
-      </c>
-      <c r="H24">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>19</v>
-      </c>
-      <c r="B25">
-        <v>99.631268436578097</v>
-      </c>
-      <c r="C25">
-        <v>0.95238095238095233</v>
-      </c>
-      <c r="D25">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="E25">
-        <v>0.88888888888888895</v>
-      </c>
-      <c r="F25">
-        <v>0.99924924924924929</v>
-      </c>
-      <c r="G25">
-        <v>0</v>
-      </c>
-      <c r="H25">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>21</v>
-      </c>
-      <c r="B26">
-        <v>98.581560283687907</v>
-      </c>
-      <c r="C26">
-        <v>1</v>
-      </c>
-      <c r="D26">
-        <v>0.5</v>
-      </c>
-      <c r="E26">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F26">
-        <v>1</v>
-      </c>
-      <c r="G26">
-        <v>0</v>
-      </c>
-      <c r="H26">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>23</v>
-      </c>
-      <c r="B27">
-        <v>92.5</v>
-      </c>
-      <c r="C27">
-        <v>1</v>
-      </c>
-      <c r="D27">
-        <v>0.25</v>
-      </c>
-      <c r="E27">
-        <v>0.4</v>
-      </c>
-      <c r="F27">
-        <v>1</v>
-      </c>
-      <c r="G27">
-        <v>0</v>
-      </c>
-      <c r="H27">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>25</v>
-      </c>
-      <c r="B28">
-        <v>92.523364485981304</v>
-      </c>
-      <c r="C28" t="e">
+      <c r="E29">
+        <v>0.74999999999999989</v>
+      </c>
+      <c r="F29">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>30</v>
+      </c>
+      <c r="B30">
+        <v>90.47619048</v>
+      </c>
+      <c r="C30">
+        <v>0</v>
+      </c>
+      <c r="D30">
+        <v>0</v>
+      </c>
+      <c r="E30" t="e">
         <v>#DIV/0!</v>
       </c>
-      <c r="D28">
-        <v>0</v>
-      </c>
-      <c r="E28" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F28">
-        <v>1</v>
-      </c>
-      <c r="G28">
-        <v>0</v>
-      </c>
-      <c r="H28">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>26</v>
-      </c>
-      <c r="B29">
-        <v>87.878787878787804</v>
-      </c>
-      <c r="C29">
-        <v>0.5</v>
-      </c>
-      <c r="D29">
-        <v>0.5</v>
-      </c>
-      <c r="E29">
-        <v>0.5</v>
-      </c>
-      <c r="F29">
-        <v>0.93103448275862066</v>
-      </c>
-      <c r="G29">
-        <v>10</v>
-      </c>
-      <c r="H29">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>28</v>
-      </c>
-      <c r="B30">
-        <v>100</v>
-      </c>
-      <c r="C30">
-        <v>1</v>
-      </c>
-      <c r="D30">
-        <v>1</v>
-      </c>
-      <c r="E30">
-        <v>1</v>
-      </c>
       <c r="F30">
-        <v>1</v>
-      </c>
-      <c r="G30">
-        <v>0</v>
-      </c>
-      <c r="H30">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+        <v>0.45238095238095238</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B31">
-        <v>94.117647059999996</v>
+        <v>95.198405510000001</v>
       </c>
       <c r="C31">
-        <v>1</v>
+        <v>0.50398406374501992</v>
       </c>
       <c r="D31">
-        <v>0.6</v>
+        <v>0.50398406374501992</v>
       </c>
       <c r="E31">
-        <v>0.74999999999999989</v>
+        <v>0.50398406374501992</v>
       </c>
       <c r="F31">
-        <v>1</v>
-      </c>
-      <c r="G31">
-        <v>0</v>
-      </c>
-      <c r="H31">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>30</v>
-      </c>
-      <c r="B32">
-        <v>90.47619048</v>
-      </c>
-      <c r="C32">
-        <v>0</v>
-      </c>
-      <c r="D32" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E32" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F32">
-        <v>0.90476190476190477</v>
-      </c>
-      <c r="G32">
-        <v>0</v>
-      </c>
-      <c r="H32">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>32</v>
-      </c>
-      <c r="B33">
-        <v>95.198405510000001</v>
-      </c>
-      <c r="C33">
-        <v>0.50398406374501992</v>
-      </c>
-      <c r="D33">
-        <v>0.94052044609665431</v>
-      </c>
-      <c r="E33">
-        <v>0.6562905317769131</v>
-      </c>
-      <c r="F33">
-        <v>0.95257142857142862</v>
-      </c>
-      <c r="G33">
-        <v>0</v>
-      </c>
-      <c r="H33">
-        <v>40</v>
+        <v>0.72827774615822427</v>
       </c>
     </row>
   </sheetData>
